--- a/agent_runs/manjidiwang/episodes/ep02/storyboard_index.xlsx
+++ b/agent_runs/manjidiwang/episodes/ep02/storyboard_index.xlsx
@@ -84,7 +84,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>书房查账 （，总时长：12秒，镜头数：4个）</t>
+          <t>书房查账</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -132,7 +132,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>敲门警觉 （，总时长：10秒，镜头数：4个）</t>
+          <t>敲门警觉</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -180,7 +180,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>门口对峙 （，总时长：12秒，镜头数：5个）</t>
+          <t>门口对峙</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -228,7 +228,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>揭穿威慑 （，总时长：12秒，镜头数：6个）</t>
+          <t>揭穿威慑</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -276,7 +276,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>逃跑与收尾 （，总时长：10秒，镜头数：4个）</t>
+          <t>逃跑与收尾</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -324,7 +324,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>父亲归来 （，总时长：15秒，镜头数：7个）</t>
+          <t>父亲归来</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -372,7 +372,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>秘书退下与杀招揭秘 （，总时长：10秒，镜头数：5个）</t>
+          <t>秘书退下与杀招揭秘</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -420,7 +420,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>愤怒与淡定 （，总时长：10秒，镜头数：5个）</t>
+          <t>愤怒与淡定</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -468,7 +468,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>提亲决断 （，总时长：10秒，镜头数：5个）</t>
+          <t>提亲决断</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>震惊与底牌 （，总时长：10秒，镜头数：5个）</t>
+          <t>震惊与底牌</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
